--- a/docs/data/jp/xlsx/6988.xlsx
+++ b/docs/data/jp/xlsx/6988.xlsx
@@ -1130,7 +1130,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>인더스트리얼 테이프</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1388,7 +1388,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>옵트로닉스</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -1646,7 +1646,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>휴먼라이프</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -6232,7 +6232,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss Before Tax</t>
+          <t>법인세비용차감전 당기이익</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
@@ -6275,7 +6275,7 @@
     <row r="88">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization Ope CF</t>
+          <t>감가상각비 및 상각비</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
@@ -6361,7 +6361,7 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Defined Benefit Liabilities</t>
+          <t>확정급여부채 증감액</t>
         </is>
       </c>
       <c r="P90" s="20" t="n">
@@ -6374,7 +6374,7 @@
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Defined Benefit Liabilities Ope CF</t>
+          <t>확정급여부채 증감액</t>
         </is>
       </c>
       <c r="F91" s="20" t="n">
@@ -6414,7 +6414,7 @@
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Trade And Other Receivables2Ope CF</t>
+          <t>매출채권 및 기타채권 증감액</t>
         </is>
       </c>
       <c r="F92" s="20" t="n">
@@ -6457,7 +6457,7 @@
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Inventories Ope CF</t>
+          <t>재고자산 증감액</t>
         </is>
       </c>
       <c r="F93" s="20" t="n">
@@ -6500,7 +6500,7 @@
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Trade And Other Payables2Ope CF</t>
+          <t>매입채무 및 기타채무 증감액</t>
         </is>
       </c>
       <c r="F94" s="20" t="n">
@@ -6543,7 +6543,7 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Advances Received Ope CFIFRS</t>
+          <t>선수금 증감액</t>
         </is>
       </c>
       <c r="S95" s="20" t="n">
@@ -6559,7 +6559,7 @@
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Advances Received Ope CF</t>
+          <t>선수금 증감액</t>
         </is>
       </c>
       <c r="F96" s="20" t="n">
@@ -6587,7 +6587,7 @@
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>Interest And Dividends Received Ope CF</t>
+          <t>이자 및 배당금 수령액</t>
         </is>
       </c>
       <c r="F97" s="20" t="n">
@@ -6673,7 +6673,7 @@
     <row r="99">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>Income Taxes Refund Paid Ope CF</t>
+          <t>법인세 등 지급액 또는 환급액</t>
         </is>
       </c>
       <c r="F99" s="20" t="n">
@@ -6802,7 +6802,7 @@
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>Purchase Of Property Plant And Equipment And Intangible Assets Inv CF</t>
+          <t>유형·무형자산 취득 지출</t>
         </is>
       </c>
       <c r="F102" s="20" t="n">
@@ -6845,7 +6845,7 @@
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Property Plant And Equipment And Intangible Assets Inv CF</t>
+          <t>유형·무형자산 처분 수입</t>
         </is>
       </c>
       <c r="F103" s="20" t="n">
@@ -6888,7 +6888,7 @@
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Time Deposits Inv CF</t>
+          <t>정기예금 증감액</t>
         </is>
       </c>
       <c r="F104" s="20" t="n">
@@ -7184,7 +7184,7 @@
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Short Term Borrowings Fin CF</t>
+          <t>단기차입금 순증감액</t>
         </is>
       </c>
       <c r="F112" s="20" t="n">
@@ -7243,7 +7243,7 @@
     <row r="114">
       <c r="A114" s="18" t="inlineStr">
         <is>
-          <t>Repayments Of Lease Obligations Fin CF</t>
+          <t>리스부채 상환 지출</t>
         </is>
       </c>
       <c r="F114" s="20" t="n">
@@ -7283,7 +7283,7 @@
     <row r="115">
       <c r="A115" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Treasury Shares Fin CF</t>
+          <t>자기주식 증감액</t>
         </is>
       </c>
       <c r="F115" s="20" t="n">
@@ -7455,7 +7455,7 @@
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
         <is>
-          <t>Effect Of Exchange Rate Changes On Cash And Cash Equivalents</t>
+          <t>현금및현금성자산 외화환산 영향액</t>
         </is>
       </c>
       <c r="F119" s="20" t="n">
@@ -7498,7 +7498,7 @@
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>Cash And Cash Equivalents Included In Assets Held For Sale In The Opening Balance</t>
+          <t>매각예정 자산에 포함된 현금및현금성자산</t>
         </is>
       </c>
       <c r="P120" s="20" t="n">
@@ -7511,7 +7511,7 @@
     <row r="121">
       <c r="A121" s="18" t="inlineStr">
         <is>
-          <t>Cash And Cash Equivalents Included In Assets Held For Sale</t>
+          <t>매각예정 자산에 포함된 현금및현금성자산</t>
         </is>
       </c>
       <c r="F121" s="20" t="n">
@@ -7530,7 +7530,7 @@
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>Reclassification Of Cash And Cash Equivalents Included In Assets Held For Sale In The Opening Balance</t>
+          <t>매각예정 자산 포함 현금및현금성자산 환입액</t>
         </is>
       </c>
       <c r="F122" s="20" t="n">
@@ -7561,7 +7561,7 @@
     <row r="123">
       <c r="A123" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Cash And Cash Equivalents</t>
+          <t>현금및현금성자산 증감액</t>
         </is>
       </c>
       <c r="F123" s="20" t="n">
@@ -10200,7 +10200,7 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>Cash And Cash Equivalents</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="C71" s="20" t="n">
@@ -10228,7 +10228,7 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>Trade And Other Receivables2CA</t>
+          <t>매출채권 및 기타채권</t>
         </is>
       </c>
       <c r="C72" s="20" t="n">
@@ -10284,7 +10284,7 @@
     <row r="74">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>Other Financial Assets CA</t>
+          <t>기타금융자산</t>
         </is>
       </c>
       <c r="C74" s="20" t="n">
@@ -10312,7 +10312,7 @@
     <row r="75">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>Other Current Assets CA</t>
+          <t>기타유동자산</t>
         </is>
       </c>
       <c r="C75" s="20" t="n">
@@ -10356,7 +10356,7 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>Assets Held For Sale</t>
+          <t>매각예정 자산</t>
         </is>
       </c>
       <c r="H77" s="20" t="n">
@@ -10484,7 +10484,7 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>무형자산</t>
         </is>
       </c>
       <c r="C82" s="20" t="n">
@@ -10512,7 +10512,7 @@
     <row r="83">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>Investments Accounted For Using Equity Method</t>
+          <t>지분법 투자</t>
         </is>
       </c>
       <c r="C83" s="20" t="n">
@@ -10540,7 +10540,7 @@
     <row r="84">
       <c r="A84" s="18" t="inlineStr">
         <is>
-          <t>Financial Assets</t>
+          <t>금융자산</t>
         </is>
       </c>
       <c r="C84" s="20" t="n">
@@ -10596,7 +10596,7 @@
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>Other Non Current Assets NCA</t>
+          <t>기타비유동자산</t>
         </is>
       </c>
       <c r="C86" s="20" t="n">
@@ -10624,7 +10624,7 @@
     <row r="87">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>Non Current Assets</t>
+          <t>비유동자산 합계</t>
         </is>
       </c>
       <c r="C87" s="20" t="n">
@@ -10680,7 +10680,7 @@
     <row r="89">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>Trade And Other Payables2CL</t>
+          <t>매입채무 및 기타채무</t>
         </is>
       </c>
       <c r="C89" s="20" t="n">
@@ -10708,7 +10708,7 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>Bonds And Borrowings CL</t>
+          <t>차입금</t>
         </is>
       </c>
       <c r="C90" s="20" t="n">
@@ -10736,7 +10736,7 @@
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>Income Taxes Payable CL</t>
+          <t>미지급법인세 등</t>
         </is>
       </c>
       <c r="C91" s="20" t="n">
@@ -10764,7 +10764,7 @@
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>Other Financial Liabilities CL</t>
+          <t>기타금융부채</t>
         </is>
       </c>
       <c r="C92" s="20" t="n">
@@ -10792,7 +10792,7 @@
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>Other Current Liabilities CL</t>
+          <t>기타유동부채</t>
         </is>
       </c>
       <c r="C93" s="20" t="n">
@@ -10836,7 +10836,7 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>Liabilities Directly Associated With Assets Held For Sale</t>
+          <t>매각예정 자산 직접 관련 부채</t>
         </is>
       </c>
       <c r="H95" s="20" t="n">
@@ -10880,7 +10880,7 @@
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>Other Financial Liabilities NCL</t>
+          <t>기타금융부채</t>
         </is>
       </c>
       <c r="C97" s="20" t="n">
@@ -10908,7 +10908,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Defined Benefit Liability NCL</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="C98" s="20" t="n">
@@ -10964,7 +10964,7 @@
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>Other Non Current Liabilities NCL</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="C100" s="20" t="n">
@@ -10992,7 +10992,7 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>Non Current Labilities</t>
+          <t>비유동부채 합계</t>
         </is>
       </c>
       <c r="C101" s="20" t="n">
@@ -11160,7 +11160,7 @@
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
-          <t>Other Components Of Equity</t>
+          <t>기타자본구성요소</t>
         </is>
       </c>
       <c r="C107" s="20" t="n">
@@ -11188,7 +11188,7 @@
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>Equity Attributable To Owners Of Parent</t>
+          <t>지배기업 소유주 귀속 지분 합계</t>
         </is>
       </c>
       <c r="C108" s="20" t="n">
@@ -11216,7 +11216,7 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>Non Controlling Interests</t>
+          <t>비지배지분</t>
         </is>
       </c>
       <c r="C109" s="20" t="n">
@@ -11244,7 +11244,7 @@
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>자본 합계</t>
         </is>
       </c>
       <c r="C110" s="20" t="n">
@@ -11272,7 +11272,7 @@
     <row r="111">
       <c r="A111" s="18" t="inlineStr">
         <is>
-          <t>Liabilities And Equity</t>
+          <t>부채및자본 합계</t>
         </is>
       </c>
       <c r="C111" s="20" t="n">
